--- a/jpcore-r4/feature/add_coverage_identifier/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/feature/add_coverage_identifier/StructureDefinition-jp-coverage.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2613" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2958" uniqueCount="504">
   <si>
     <t>Property</t>
   </si>
@@ -552,8 +552,280 @@
     <t>Business Identifier for the coverage　このカバレッジに割り当てられた一意の識別子【詳細参照】</t>
   </si>
   <si>
-    <t>A unique identifier assigned to this coverage.  
-このカバレッジに割り当てられた一意の識別子。</t>
+    <t>A unique identifier assigned to this coverage.  このカバレッジに割り当てられた一意の識別子。</t>
+  </si>
+  <si>
+    <t>Allows coverages to be distinguished and referenced.  
+カバレッジを区別して参照できるようにする。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:system}
+</t>
+  </si>
+  <si>
+    <t>Event.identifier</t>
+  </si>
+  <si>
+    <t>.id</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>C02</t>
+  </si>
+  <si>
+    <t>IN1-2</t>
+  </si>
+  <si>
+    <t>C.32, C.33, C.39</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier</t>
+  </si>
+  <si>
+    <t>insuranceIdentifier</t>
+  </si>
+  <si>
+    <t>被保険者識別子</t>
+  </si>
+  <si>
+    <t>被保険者識別子として、保険者情報と被保険者情報を以下の仕様で連結したひとつの文字列を使用する</t>
+  </si>
+  <si>
+    <t>「被保険者識別子」の文字列仕様(StructureDefinition_JP_Coverage.html#「被保険者識別子」の文字列仕様)を参照のこと</t>
+  </si>
+  <si>
+    <t>カバレッジを区別し、参照することができます。 / Allows coverages to be distinguished and referenced.</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.id</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.extension</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.extension</t>
+  </si>
+  <si>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.use</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.use</t>
+  </si>
+  <si>
+    <t>通常|公式|温度|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>この識別子の目的。 / The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>アプリケーションは、識別子が一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>特定の使用のコンテキストが一連の識別子の中から選択される適切な識別子を許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>既知の場合、この識別子の目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.type</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>識別子の説明 / Description of identifier</t>
+  </si>
+  <si>
+    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>この要素は、識別子の一般的なカテゴリのみを扱います。識別子。システムに対応するコードに使用しないでください。一部の識別子は、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明な識別子を処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>識別子システムが不明な場合、ユーザーは識別子を使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.system</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.system</t>
+  </si>
+  <si>
+    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/Idsystem/JP_Insurance_SubscriberID</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.value</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.value</t>
+  </si>
+  <si>
+    <t>被保険者識別子の値を格納</t>
+  </si>
+  <si>
+    <t>被保険者識別子として、保険者情報と被保険者情報とを以下の仕様で連結したひとつの文字列を使用する。  
+本仕様では、以下、これを「被保険者個人識別子」と称する。また英数字は１バイト系文字の英数字を指す。  
+被保険者個人識別子:以下の各情報（要素）を半角コロン（文字コード１６進数 5A）で結合する。  
+要素を省略する、とある場合には、長さ０の文字列とする。「被保険者識別子」の文字列仕様(StructureDefinition_JP_Coverage.html#「被保険者識別子」の文字列仕様)を参照のこと</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.period</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>識別子が使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceIdentifier.assigner</t>
+  </si>
+  <si>
+    <t>Coverage.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
+</t>
+  </si>
+  <si>
+    <t>保険者情報を設定</t>
+  </si>
+  <si>
+    <t>保険者情報として[JP_Organization](StructureDefinition-jp-organization.html)を設定する。</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier</t>
+  </si>
+  <si>
+    <t>insuranceCsvIdentifier</t>
+  </si>
+  <si>
+    <t>被保険者識別子（CSV形式）　"１２－３４","５６７８","00"</t>
+  </si>
+  <si>
+    <t>被保険者識別子として、保険者情報と被保険者情報をカンマ区切りにて連結する</t>
   </si>
   <si>
     <t>The main (and possibly only) identifier for the coverage - often referred to as a Member Id, Certificate number, Personal Health Number or Case ID. May be constructed as the concatenation of the Coverage.SubscriberID and the Coverage.dependent.  
@@ -563,265 +835,36 @@
 例："１２－３４","５６７８","00"</t>
   </si>
   <si>
-    <t>Allows coverages to be distinguished and referenced.  
-カバレッジを区別して参照できるようにする。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:system}
-</t>
-  </si>
-  <si>
-    <t>Event.identifier</t>
-  </si>
-  <si>
-    <t>.id</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>C02</t>
-  </si>
-  <si>
-    <t>IN1-2</t>
-  </si>
-  <si>
-    <t>C.32, C.33, C.39</t>
-  </si>
-  <si>
-    <t>Coverage.identifier:insuranceIdentifier</t>
-  </si>
-  <si>
-    <t>insuranceIdentifier</t>
-  </si>
-  <si>
-    <t>被保険者識別子</t>
-  </si>
-  <si>
-    <t>被保険者識別子として、保険者情報と被保険者情報とを以下の仕様で連結したひとつの文字列を使用する</t>
-  </si>
-  <si>
-    <t>「被保険者識別子」の文字列仕様(StructureDefinition_JP_Coverage.html#「被保険者識別子」の文字列仕様)を参照のこと</t>
-  </si>
-  <si>
-    <t>カバレッジを区別し、参照することができます。 / Allows coverages to be distinguished and referenced.</t>
-  </si>
-  <si>
-    <t>Coverage.identifier:insuranceIdentifier.id</t>
-  </si>
-  <si>
-    <t>Coverage.identifier.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Coverage.identifier:insuranceIdentifier.extension</t>
-  </si>
-  <si>
-    <t>Coverage.identifier.extension</t>
-  </si>
-  <si>
-    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Coverage.identifier:insuranceIdentifier.use</t>
-  </si>
-  <si>
-    <t>Coverage.identifier.use</t>
-  </si>
-  <si>
-    <t>通常|公式|温度|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>この識別子の目的。 / The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>アプリケーションは、識別子が一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>特定の使用のコンテキストが一連の識別子の中から選択される適切な識別子を許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>既知の場合、この識別子の目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>Coverage.identifier:insuranceIdentifier.type</t>
-  </si>
-  <si>
-    <t>Coverage.identifier.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>識別子の説明 / Description of identifier</t>
-  </si>
-  <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>この要素は、識別子の一般的なカテゴリのみを扱います。識別子。システムに対応するコードに使用しないでください。一部の識別子は、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明な識別子を処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>識別子システムが不明な場合、ユーザーは識別子を使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
-    <t>Coverage.identifier:insuranceIdentifier.system</t>
-  </si>
-  <si>
-    <t>Coverage.identifier.system</t>
-  </si>
-  <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/Idsystem/JP_Insurance_SubscriberID</t>
-  </si>
-  <si>
-    <t>Identifier.system</t>
-  </si>
-  <si>
-    <t>II.root or Role.id.root</t>
-  </si>
-  <si>
-    <t>CX.4 / EI-2-4</t>
-  </si>
-  <si>
-    <t>Coverage.identifier:insuranceIdentifier.value</t>
-  </si>
-  <si>
-    <t>Coverage.identifier.value</t>
-  </si>
-  <si>
-    <t>被保険者識別子の値を格納</t>
-  </si>
-  <si>
-    <t>被保険者識別子として、保険者情報と被保険者情報とを以下の仕様で連結したひとつの文字列を使用する。  
-本仕様では、以下、これを「被保険者個人識別子」と称する。また英数字は１バイト系文字の英数字を指す。  
-被保険者個人識別子:以下の各情報（要素）を半角コロン（文字コード１６進数 5A）で結合する。  
+    <t>Coverage.identifier:insuranceCsvIdentifier.id</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier.extension</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier.use</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier.type</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier.system</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier.value</t>
+  </si>
+  <si>
+    <t>The main (and possibly only) identifier for the coverage - often referred to as a Member Id, Certificate number, Personal Health Number or Case ID. May be constructed as the concatenation of the Coverage.SubscriberID and the Coverage.dependent.  
+カバレッジのメイン（および場合によっては唯一の）識別子-多くの場合、メンバID、証明書番号、個人の健康番号、またはケースIDと呼ばれる。  
+【JP Core仕様】被保険者記号と番号と枝番を全角にした上でダブルコーテーションで囲い、カンマ区切りで連結する。  
+ルール："{保険者番号:半角英数８桁}","{被保険者記号}","{被保険者番号}","{枝番:半角数字２桁}"  
+例："00012345","１２－３４","５６７８","00"
 要素を省略する、とある場合には、長さ０の文字列とする。「被保険者識別子」の文字列仕様(StructureDefinition_JP_Coverage.html#「被保険者識別子」の文字列仕様)を参照のこと</t>
   </si>
   <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>Identifier.value</t>
-  </si>
-  <si>
-    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>CX.1 / EI.1</t>
-  </si>
-  <si>
-    <t>Coverage.identifier:insuranceIdentifier.period</t>
-  </si>
-  <si>
-    <t>Coverage.identifier.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
-    <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>識別子が使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
-  </si>
-  <si>
-    <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>Role.effectiveTime or implied by context</t>
-  </si>
-  <si>
-    <t>CX.7 + CX.8</t>
-  </si>
-  <si>
-    <t>Coverage.identifier:insuranceIdentifier.assigner</t>
-  </si>
-  <si>
-    <t>Coverage.identifier.assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
-</t>
-  </si>
-  <si>
-    <t>保険者情報を設定</t>
-  </si>
-  <si>
-    <t>保険者情報として[JP_Organization](StructureDefinition-jp-organization.html)を設定する。</t>
-  </si>
-  <si>
-    <t>Identifier.assigner</t>
-  </si>
-  <si>
-    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
-  </si>
-  <si>
-    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+    <t>Coverage.identifier:insuranceCsvIdentifier.period</t>
+  </si>
+  <si>
+    <t>Coverage.identifier:insuranceCsvIdentifier.assigner</t>
   </si>
   <si>
     <t>Coverage.status</t>
@@ -1931,7 +1974,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP67"/>
+  <dimension ref="A1:AP76"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.57421875" customWidth="true" bestFit="true"/>
@@ -3584,10 +3627,10 @@
         <v>171</v>
       </c>
       <c r="N14" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O14" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>80</v>
@@ -3624,7 +3667,7 @@
         <v>80</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
@@ -3649,33 +3692,33 @@
         <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AM14" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="AO14" t="s" s="2">
+      <c r="AP14" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="AP14" t="s" s="2">
-        <v>180</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>168</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>80</v>
@@ -3700,16 +3743,16 @@
         <v>169</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>186</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>80</v>
@@ -3773,30 +3816,30 @@
         <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AL15" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="AL15" t="s" s="2">
+      <c r="AM15" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AM15" t="s" s="2">
+      <c r="AN15" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="AN15" t="s" s="2">
+      <c r="AO15" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="AO15" t="s" s="2">
+      <c r="AP15" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>180</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3819,13 +3862,13 @@
         <v>80</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3876,25 +3919,25 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>80</v>
@@ -3911,10 +3954,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3940,10 +3983,10 @@
         <v>135</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="N17" t="s" s="2">
         <v>165</v>
@@ -3987,7 +4030,7 @@
         <v>138</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>80</v>
@@ -3996,7 +4039,7 @@
         <v>139</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4014,7 +4057,7 @@
         <v>80</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>80</v>
@@ -4031,10 +4074,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4060,16 +4103,16 @@
         <v>110</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -4094,31 +4137,31 @@
         <v>80</v>
       </c>
       <c r="X18" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="Y18" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="Y18" t="s" s="2">
+      <c r="Z18" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="Z18" t="s" s="2">
+      <c r="AA18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF18" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4136,7 +4179,7 @@
         <v>80</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>80</v>
@@ -4153,10 +4196,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4179,19 +4222,19 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -4216,31 +4259,31 @@
         <v>80</v>
       </c>
       <c r="X19" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="Y19" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="Y19" t="s" s="2">
+      <c r="Z19" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="Z19" t="s" s="2">
+      <c r="AA19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF19" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4258,7 +4301,7 @@
         <v>80</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>80</v>
@@ -4267,7 +4310,7 @@
         <v>80</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>80</v>
@@ -4275,10 +4318,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4304,65 +4347,65 @@
         <v>104</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF20" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="S20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4380,16 +4423,16 @@
         <v>80</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>80</v>
@@ -4397,10 +4440,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4423,16 +4466,16 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4482,7 +4525,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4500,16 +4543,16 @@
         <v>80</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>80</v>
@@ -4517,10 +4560,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4543,13 +4586,13 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4600,7 +4643,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4618,16 +4661,16 @@
         <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>80</v>
@@ -4635,10 +4678,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4661,16 +4704,16 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="M23" t="s" s="2">
-        <v>253</v>
-      </c>
       <c r="N23" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4720,7 +4763,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4738,16 +4781,16 @@
         <v>80</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>80</v>
@@ -4755,18 +4798,20 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="C24" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="B24" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>90</v>
@@ -4775,13 +4820,13 @@
         <v>80</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>110</v>
+        <v>169</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>258</v>
@@ -4793,7 +4838,7 @@
         <v>260</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>261</v>
+        <v>185</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -4818,13 +4863,13 @@
         <v>80</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>206</v>
+        <v>80</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>80</v>
@@ -4842,13 +4887,13 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>257</v>
+        <v>168</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>80</v>
@@ -4857,30 +4902,30 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>264</v>
+        <v>174</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>265</v>
+        <v>175</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>266</v>
+        <v>176</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>80</v>
+        <v>177</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>80</v>
+        <v>178</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>80</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>267</v>
+        <v>187</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4900,23 +4945,19 @@
         <v>80</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>213</v>
+        <v>188</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>268</v>
+        <v>189</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>271</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>80</v>
       </c>
@@ -4940,13 +4981,13 @@
         <v>80</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>272</v>
+        <v>80</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>273</v>
+        <v>80</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>80</v>
@@ -4964,7 +5005,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>267</v>
+        <v>191</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4976,22 +5017,22 @@
         <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>274</v>
+        <v>80</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>275</v>
+        <v>80</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>80</v>
@@ -4999,21 +5040,21 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>276</v>
+        <v>194</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>80</v>
@@ -5022,23 +5063,21 @@
         <v>80</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>277</v>
+        <v>135</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>278</v>
+        <v>195</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>279</v>
+        <v>196</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>80</v>
       </c>
@@ -5074,57 +5113,57 @@
         <v>80</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>276</v>
+        <v>198</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>282</v>
+        <v>80</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>283</v>
+        <v>80</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>284</v>
+        <v>80</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>285</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>286</v>
+        <v>200</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5141,25 +5180,25 @@
         <v>80</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>287</v>
+        <v>110</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>288</v>
+        <v>201</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>289</v>
+        <v>202</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>290</v>
+        <v>203</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>291</v>
+        <v>204</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>80</v>
@@ -5184,13 +5223,13 @@
         <v>80</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>80</v>
+        <v>205</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>80</v>
+        <v>206</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>80</v>
+        <v>207</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>80</v>
@@ -5208,7 +5247,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>286</v>
+        <v>208</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5226,27 +5265,27 @@
         <v>80</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>80</v>
+        <v>209</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>282</v>
+        <v>80</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>283</v>
+        <v>80</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>284</v>
+        <v>133</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>285</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>292</v>
+        <v>264</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>292</v>
+        <v>211</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5269,17 +5308,19 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>293</v>
+        <v>213</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="O28" t="s" s="2">
-        <v>295</v>
+        <v>216</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>80</v>
@@ -5304,13 +5345,13 @@
         <v>80</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>80</v>
+        <v>217</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>80</v>
+        <v>218</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>80</v>
+        <v>219</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>80</v>
@@ -5328,7 +5369,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>292</v>
+        <v>220</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5346,27 +5387,27 @@
         <v>80</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>80</v>
+        <v>209</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>282</v>
+        <v>80</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>283</v>
+        <v>80</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>284</v>
+        <v>221</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>285</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>296</v>
+        <v>265</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>296</v>
+        <v>223</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5389,26 +5430,26 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>297</v>
+        <v>104</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>298</v>
+        <v>224</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>299</v>
+        <v>225</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>300</v>
+        <v>226</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>301</v>
+        <v>227</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>80</v>
+        <v>228</v>
       </c>
       <c r="S29" t="s" s="2">
         <v>80</v>
@@ -5450,10 +5491,10 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>296</v>
+        <v>229</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>90</v>
@@ -5465,30 +5506,30 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>302</v>
+        <v>80</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>80</v>
+        <v>230</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>282</v>
+        <v>80</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>283</v>
+        <v>80</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>284</v>
+        <v>231</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>285</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>303</v>
+        <v>266</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>303</v>
+        <v>233</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5511,20 +5552,18 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>304</v>
+        <v>234</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>305</v>
+        <v>267</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>307</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>80</v>
       </c>
@@ -5572,7 +5611,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>303</v>
+        <v>237</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5590,16 +5629,16 @@
         <v>80</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>80</v>
+        <v>238</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>308</v>
+        <v>80</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>309</v>
+        <v>239</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>80</v>
@@ -5607,10 +5646,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>310</v>
+        <v>268</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>310</v>
+        <v>241</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5630,23 +5669,19 @@
         <v>80</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>213</v>
+        <v>242</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>311</v>
+        <v>243</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>314</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>80</v>
       </c>
@@ -5670,13 +5705,13 @@
         <v>80</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>218</v>
+        <v>80</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>315</v>
+        <v>80</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>316</v>
+        <v>80</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>80</v>
@@ -5694,7 +5729,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>310</v>
+        <v>245</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5712,16 +5747,16 @@
         <v>80</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>80</v>
+        <v>246</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>317</v>
+        <v>80</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>80</v>
+        <v>247</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>80</v>
@@ -5729,10 +5764,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>318</v>
+        <v>269</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>318</v>
+        <v>249</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5755,20 +5790,18 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>319</v>
+        <v>251</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>320</v>
+        <v>252</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>80</v>
       </c>
@@ -5816,7 +5849,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>318</v>
+        <v>253</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5831,19 +5864,19 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>323</v>
+        <v>80</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>324</v>
+        <v>254</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>325</v>
+        <v>80</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>326</v>
+        <v>255</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>80</v>
@@ -5851,10 +5884,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>327</v>
+        <v>270</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>327</v>
+        <v>270</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5865,31 +5898,31 @@
         <v>90</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>328</v>
+        <v>110</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>329</v>
+        <v>271</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>330</v>
+        <v>272</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>331</v>
+        <v>273</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>332</v>
+        <v>274</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>80</v>
@@ -5914,13 +5947,13 @@
         <v>80</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>80</v>
+        <v>205</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>80</v>
+        <v>275</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>80</v>
+        <v>276</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>80</v>
@@ -5938,13 +5971,13 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>327</v>
+        <v>270</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>80</v>
@@ -5953,30 +5986,30 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>80</v>
+        <v>277</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>80</v>
+        <v>278</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>333</v>
+        <v>279</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>334</v>
+        <v>80</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>335</v>
+        <v>80</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>336</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>337</v>
+        <v>280</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>337</v>
+        <v>280</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5987,7 +6020,7 @@
         <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>80</v>
@@ -5996,22 +6029,22 @@
         <v>80</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>338</v>
+        <v>212</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>339</v>
+        <v>281</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>340</v>
+        <v>282</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>341</v>
+        <v>283</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>342</v>
+        <v>284</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>80</v>
@@ -6036,13 +6069,13 @@
         <v>80</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>80</v>
+        <v>285</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>80</v>
+        <v>286</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>80</v>
@@ -6060,13 +6093,13 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>337</v>
+        <v>280</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>80</v>
@@ -6081,13 +6114,13 @@
         <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>80</v>
+        <v>287</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>80</v>
+        <v>288</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>80</v>
@@ -6095,10 +6128,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>343</v>
+        <v>289</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>343</v>
+        <v>289</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6118,19 +6151,23 @@
         <v>80</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>189</v>
+        <v>290</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>190</v>
+        <v>291</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>80</v>
       </c>
@@ -6178,7 +6215,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>192</v>
+        <v>289</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6190,44 +6227,44 @@
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>193</v>
+        <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>80</v>
+        <v>295</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>80</v>
+        <v>296</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>80</v>
+        <v>297</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>80</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>344</v>
+        <v>299</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>344</v>
+        <v>299</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>162</v>
+        <v>80</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>80</v>
@@ -6236,21 +6273,23 @@
         <v>80</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>135</v>
+        <v>300</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>196</v>
+        <v>301</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>197</v>
+        <v>302</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
       </c>
@@ -6298,80 +6337,78 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>199</v>
+        <v>299</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>193</v>
+        <v>80</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>80</v>
+        <v>295</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>80</v>
+        <v>296</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>80</v>
+        <v>297</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>80</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>345</v>
+        <v>305</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>345</v>
+        <v>305</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>346</v>
+        <v>80</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J37" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>135</v>
+        <v>188</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>347</v>
+        <v>306</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>166</v>
+        <v>308</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -6420,45 +6457,45 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>349</v>
+        <v>305</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>80</v>
+        <v>295</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>80</v>
+        <v>296</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>80</v>
+        <v>297</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>80</v>
+        <v>298</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>350</v>
+        <v>309</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>350</v>
+        <v>309</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6481,19 +6518,19 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>213</v>
+        <v>310</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>351</v>
+        <v>311</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>352</v>
+        <v>312</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>353</v>
+        <v>313</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>354</v>
+        <v>314</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -6518,13 +6555,13 @@
         <v>80</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>218</v>
+        <v>80</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>355</v>
+        <v>80</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>80</v>
@@ -6542,7 +6579,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>350</v>
+        <v>309</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>90</v>
@@ -6557,30 +6594,30 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>80</v>
+        <v>315</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>80</v>
+        <v>295</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>80</v>
+        <v>296</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>80</v>
+        <v>297</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>80</v>
+        <v>298</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>357</v>
+        <v>316</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>357</v>
+        <v>316</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6588,7 +6625,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>90</v>
@@ -6603,19 +6640,19 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>358</v>
+        <v>317</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>359</v>
+        <v>318</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>360</v>
+        <v>319</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>361</v>
+        <v>320</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -6664,10 +6701,10 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>357</v>
+        <v>316</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>90</v>
@@ -6688,21 +6725,21 @@
         <v>80</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>362</v>
+        <v>321</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>363</v>
+        <v>322</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>364</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>365</v>
+        <v>323</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>365</v>
+        <v>323</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6722,20 +6759,22 @@
         <v>80</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>366</v>
+        <v>324</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="O40" t="s" s="2">
-        <v>368</v>
+        <v>327</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>80</v>
@@ -6760,13 +6799,13 @@
         <v>80</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>80</v>
+        <v>217</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>80</v>
+        <v>328</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>80</v>
+        <v>329</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>80</v>
@@ -6784,7 +6823,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>365</v>
+        <v>323</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6808,21 +6847,21 @@
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>362</v>
+        <v>330</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>363</v>
+        <v>80</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>364</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>369</v>
+        <v>331</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>369</v>
+        <v>331</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6845,19 +6884,19 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>370</v>
+        <v>242</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>371</v>
+        <v>332</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>372</v>
+        <v>333</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>373</v>
+        <v>334</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>374</v>
+        <v>335</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -6906,7 +6945,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>369</v>
+        <v>331</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6921,19 +6960,19 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>80</v>
+        <v>336</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>80</v>
+        <v>337</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>80</v>
+        <v>338</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>309</v>
+        <v>339</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>80</v>
@@ -6941,10 +6980,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>375</v>
+        <v>340</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>375</v>
+        <v>340</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6952,10 +6991,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>80</v>
@@ -6967,17 +7006,19 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>189</v>
+        <v>341</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>376</v>
+        <v>342</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="O42" t="s" s="2">
-        <v>378</v>
+        <v>345</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -7026,13 +7067,13 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>375</v>
+        <v>340</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>80</v>
@@ -7047,28 +7088,28 @@
         <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>80</v>
+        <v>346</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>379</v>
+        <v>347</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>80</v>
+        <v>348</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>80</v>
+        <v>349</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>381</v>
+        <v>80</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7087,19 +7128,19 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>382</v>
+        <v>352</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>383</v>
+        <v>353</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>384</v>
+        <v>354</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>385</v>
+        <v>355</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
@@ -7148,7 +7189,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7183,10 +7224,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>386</v>
+        <v>356</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>386</v>
+        <v>356</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7209,13 +7250,13 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7266,25 +7307,25 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>80</v>
@@ -7301,10 +7342,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>387</v>
+        <v>357</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>387</v>
+        <v>357</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7330,10 +7371,10 @@
         <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>165</v>
@@ -7386,7 +7427,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7404,7 +7445,7 @@
         <v>80</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>80</v>
@@ -7421,14 +7462,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>388</v>
+        <v>358</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>388</v>
+        <v>358</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7450,10 +7491,10 @@
         <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>165</v>
@@ -7508,7 +7549,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7543,10 +7584,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7554,7 +7595,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>90</v>
@@ -7569,19 +7610,19 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>390</v>
+        <v>364</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>392</v>
+        <v>366</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -7606,13 +7647,13 @@
         <v>80</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>394</v>
+        <v>368</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>395</v>
+        <v>369</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>80</v>
@@ -7630,10 +7671,10 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>90</v>
@@ -7665,10 +7706,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>396</v>
+        <v>370</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>396</v>
+        <v>370</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7676,7 +7717,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>90</v>
@@ -7688,19 +7729,23 @@
         <v>80</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>190</v>
+        <v>371</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
       </c>
@@ -7748,10 +7793,10 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>192</v>
+        <v>370</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>90</v>
@@ -7760,44 +7805,44 @@
         <v>80</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>193</v>
+        <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>80</v>
+        <v>375</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>80</v>
+        <v>376</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>80</v>
+        <v>377</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>162</v>
+        <v>80</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>80</v>
@@ -7806,21 +7851,21 @@
         <v>80</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>135</v>
+        <v>188</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>196</v>
+        <v>379</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
       </c>
@@ -7856,57 +7901,57 @@
         <v>80</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>199</v>
+        <v>378</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>193</v>
+        <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>80</v>
+        <v>375</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>80</v>
+        <v>376</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>80</v>
+        <v>377</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7917,7 +7962,7 @@
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>80</v>
@@ -7929,19 +7974,19 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>399</v>
+        <v>383</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>400</v>
+        <v>384</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>401</v>
+        <v>385</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>402</v>
+        <v>386</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>403</v>
+        <v>387</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -7990,13 +8035,13 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>404</v>
+        <v>382</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>80</v>
@@ -8008,7 +8053,7 @@
         <v>80</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>405</v>
+        <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>80</v>
@@ -8017,7 +8062,7 @@
         <v>80</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>406</v>
+        <v>322</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>80</v>
@@ -8025,10 +8070,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>407</v>
+        <v>388</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>407</v>
+        <v>388</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8048,19 +8093,21 @@
         <v>80</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>190</v>
+        <v>389</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>191</v>
+        <v>390</v>
       </c>
       <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
       </c>
@@ -8108,7 +8155,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>192</v>
+        <v>388</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8120,19 +8167,19 @@
         <v>80</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>193</v>
+        <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>80</v>
+        <v>392</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>80</v>
@@ -8143,14 +8190,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>162</v>
+        <v>394</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8169,18 +8216,20 @@
         <v>80</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>135</v>
+        <v>351</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>196</v>
+        <v>395</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>197</v>
+        <v>396</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
       </c>
@@ -8216,19 +8265,19 @@
         <v>80</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>199</v>
+        <v>393</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8240,13 +8289,13 @@
         <v>80</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>193</v>
+        <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>80</v>
@@ -8263,10 +8312,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8286,23 +8335,19 @@
         <v>80</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>104</v>
+        <v>188</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>410</v>
+        <v>189</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>80</v>
       </c>
@@ -8350,7 +8395,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>414</v>
+        <v>191</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8362,13 +8407,13 @@
         <v>80</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>415</v>
+        <v>192</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>80</v>
@@ -8377,7 +8422,7 @@
         <v>80</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>416</v>
+        <v>80</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>80</v>
@@ -8385,21 +8430,21 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>80</v>
@@ -8408,19 +8453,19 @@
         <v>80</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>189</v>
+        <v>135</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>418</v>
+        <v>195</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>419</v>
+        <v>196</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>420</v>
+        <v>165</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8470,25 +8515,25 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>421</v>
+        <v>198</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>422</v>
+        <v>192</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>80</v>
@@ -8497,7 +8542,7 @@
         <v>80</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>423</v>
+        <v>80</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>80</v>
@@ -8505,45 +8550,45 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>424</v>
+        <v>401</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>424</v>
+        <v>401</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>80</v>
+        <v>359</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>425</v>
+        <v>360</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>426</v>
+        <v>361</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>427</v>
+        <v>165</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>428</v>
+        <v>166</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -8592,25 +8637,25 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>429</v>
+        <v>362</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>430</v>
+        <v>133</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>80</v>
@@ -8619,7 +8664,7 @@
         <v>80</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>431</v>
+        <v>80</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>80</v>
@@ -8627,10 +8672,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>432</v>
+        <v>402</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>432</v>
+        <v>402</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8653,17 +8698,19 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>433</v>
+        <v>403</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="O56" t="s" s="2">
-        <v>435</v>
+        <v>406</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>80</v>
@@ -8688,13 +8735,13 @@
         <v>80</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>80</v>
+        <v>217</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>80</v>
+        <v>407</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>80</v>
+        <v>408</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>80</v>
@@ -8712,7 +8759,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>436</v>
+        <v>402</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8730,7 +8777,7 @@
         <v>80</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>437</v>
+        <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>80</v>
@@ -8739,7 +8786,7 @@
         <v>80</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>438</v>
+        <v>80</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>80</v>
@@ -8747,10 +8794,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>439</v>
+        <v>409</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>439</v>
+        <v>409</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8770,23 +8817,19 @@
         <v>80</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>440</v>
+        <v>188</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>441</v>
+        <v>189</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>444</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>80</v>
       </c>
@@ -8834,7 +8877,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>445</v>
+        <v>191</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8846,13 +8889,13 @@
         <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>446</v>
+        <v>192</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>80</v>
@@ -8861,7 +8904,7 @@
         <v>80</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>447</v>
+        <v>80</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>80</v>
@@ -8869,21 +8912,21 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>448</v>
+        <v>410</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>448</v>
+        <v>410</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>80</v>
@@ -8892,23 +8935,21 @@
         <v>80</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>189</v>
+        <v>135</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>449</v>
+        <v>195</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>450</v>
+        <v>196</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>452</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>80</v>
       </c>
@@ -8944,37 +8985,37 @@
         <v>80</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>453</v>
+        <v>198</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>454</v>
+        <v>192</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>80</v>
@@ -8983,7 +9024,7 @@
         <v>80</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>455</v>
+        <v>80</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>80</v>
@@ -8991,10 +9032,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>456</v>
+        <v>411</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>456</v>
+        <v>411</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9002,10 +9043,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>80</v>
@@ -9017,19 +9058,19 @@
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>457</v>
+        <v>412</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>458</v>
+        <v>413</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>459</v>
+        <v>414</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>460</v>
+        <v>415</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>461</v>
+        <v>416</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
@@ -9078,13 +9119,13 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>456</v>
+        <v>417</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>80</v>
@@ -9096,27 +9137,27 @@
         <v>80</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>80</v>
+        <v>418</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>362</v>
+        <v>80</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>363</v>
+        <v>419</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>364</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>462</v>
+        <v>420</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>462</v>
+        <v>420</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9127,7 +9168,7 @@
         <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>80</v>
@@ -9139,18 +9180,16 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>338</v>
+        <v>188</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>463</v>
+        <v>189</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>464</v>
+        <v>190</v>
       </c>
       <c r="N60" s="2"/>
-      <c r="O60" t="s" s="2">
-        <v>385</v>
-      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>80</v>
       </c>
@@ -9198,25 +9237,25 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>462</v>
+        <v>191</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>80</v>
@@ -9233,21 +9272,21 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>465</v>
+        <v>421</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>465</v>
+        <v>421</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>80</v>
@@ -9259,15 +9298,17 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>189</v>
+        <v>135</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>80</v>
@@ -9304,37 +9345,37 @@
         <v>80</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="AF61" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL61" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>80</v>
@@ -9351,21 +9392,21 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>466</v>
+        <v>422</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>466</v>
+        <v>422</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>162</v>
+        <v>80</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>80</v>
@@ -9374,21 +9415,23 @@
         <v>80</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>196</v>
+        <v>423</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>197</v>
+        <v>424</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>425</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>426</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>80</v>
       </c>
@@ -9436,25 +9479,25 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>199</v>
+        <v>427</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>193</v>
+        <v>428</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>80</v>
@@ -9463,7 +9506,7 @@
         <v>80</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>80</v>
+        <v>429</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>80</v>
@@ -9471,46 +9514,44 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>467</v>
+        <v>430</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>467</v>
+        <v>430</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>346</v>
+        <v>80</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J63" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>135</v>
+        <v>188</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>347</v>
+        <v>431</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>348</v>
+        <v>432</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>80</v>
       </c>
@@ -9558,25 +9599,25 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>349</v>
+        <v>434</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>133</v>
+        <v>435</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>80</v>
@@ -9585,7 +9626,7 @@
         <v>80</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>80</v>
+        <v>436</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>80</v>
@@ -9593,10 +9634,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>468</v>
+        <v>437</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>468</v>
+        <v>437</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9604,7 +9645,7 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>90</v>
@@ -9619,17 +9660,19 @@
         <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>213</v>
+        <v>110</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>469</v>
+        <v>438</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>439</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>440</v>
+      </c>
       <c r="O64" t="s" s="2">
-        <v>471</v>
+        <v>441</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>80</v>
@@ -9654,13 +9697,13 @@
         <v>80</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>472</v>
+        <v>80</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>473</v>
+        <v>80</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>474</v>
+        <v>80</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>80</v>
@@ -9678,10 +9721,10 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>468</v>
+        <v>442</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>90</v>
@@ -9696,7 +9739,7 @@
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>80</v>
+        <v>443</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>80</v>
@@ -9705,7 +9748,7 @@
         <v>80</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>80</v>
+        <v>444</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>80</v>
@@ -9713,10 +9756,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>475</v>
+        <v>445</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>475</v>
+        <v>445</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9739,17 +9782,17 @@
         <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>243</v>
+        <v>188</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>476</v>
+        <v>446</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>477</v>
+        <v>447</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>478</v>
+        <v>448</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -9798,7 +9841,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>475</v>
+        <v>449</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9816,7 +9859,7 @@
         <v>80</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>80</v>
+        <v>450</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>80</v>
@@ -9825,7 +9868,7 @@
         <v>80</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>80</v>
+        <v>451</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>80</v>
@@ -9833,10 +9876,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>479</v>
+        <v>452</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>479</v>
+        <v>452</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9856,22 +9899,22 @@
         <v>80</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>480</v>
+        <v>454</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>481</v>
+        <v>455</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>483</v>
+        <v>457</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>80</v>
@@ -9920,7 +9963,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>479</v>
+        <v>458</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -9938,7 +9981,7 @@
         <v>80</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>80</v>
+        <v>459</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>80</v>
@@ -9947,7 +9990,7 @@
         <v>80</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>80</v>
+        <v>460</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>80</v>
@@ -9955,10 +9998,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>484</v>
+        <v>461</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>484</v>
+        <v>461</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9969,7 +10012,7 @@
         <v>81</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>80</v>
@@ -9978,22 +10021,22 @@
         <v>80</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>485</v>
+        <v>188</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>486</v>
+        <v>462</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>487</v>
+        <v>463</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>488</v>
+        <v>464</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>489</v>
+        <v>465</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>80</v>
@@ -10042,13 +10085,13 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>484</v>
+        <v>466</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>80</v>
@@ -10060,19 +10103,1105 @@
         <v>80</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>193</v>
+        <v>467</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>283</v>
+        <v>80</v>
       </c>
       <c r="AO67" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="AP67" t="s" s="2">
-        <v>285</v>
+      <c r="N74" s="2"/>
+      <c r="O74" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AP76" t="s" s="2">
+        <v>298</v>
       </c>
     </row>
   </sheetData>

--- a/jpcore-r4/feature/add_coverage_identifier/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/feature/add_coverage_identifier/StructureDefinition-jp-coverage.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2958" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2958" uniqueCount="505">
   <si>
     <t>Property</t>
   </si>
@@ -848,6 +848,9 @@
   </si>
   <si>
     <t>Coverage.identifier:insuranceCsvIdentifier.system</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/Idsystem/JP_Insurance_SubscriberCsvID</t>
   </si>
   <si>
     <t>Coverage.identifier:insuranceCsvIdentifier.value</t>
@@ -5449,7 +5452,7 @@
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>228</v>
+        <v>266</v>
       </c>
       <c r="S29" t="s" s="2">
         <v>80</v>
@@ -5526,7 +5529,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>233</v>
@@ -5558,7 +5561,7 @@
         <v>234</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>236</v>
@@ -5646,7 +5649,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>241</v>
@@ -5764,7 +5767,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>249</v>
@@ -5884,10 +5887,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5913,16 +5916,16 @@
         <v>110</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>80</v>
@@ -5950,10 +5953,10 @@
         <v>205</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>80</v>
@@ -5971,7 +5974,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>90</v>
@@ -5986,13 +5989,13 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>80</v>
@@ -6006,10 +6009,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6035,16 +6038,16 @@
         <v>212</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>80</v>
@@ -6072,10 +6075,10 @@
         <v>114</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>80</v>
@@ -6093,7 +6096,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6114,13 +6117,13 @@
         <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>80</v>
@@ -6128,10 +6131,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6154,19 +6157,19 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>80</v>
@@ -6215,7 +6218,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6236,24 +6239,24 @@
         <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6276,19 +6279,19 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
@@ -6337,7 +6340,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6358,24 +6361,24 @@
         <v>80</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6401,14 +6404,14 @@
         <v>188</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -6457,7 +6460,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6478,24 +6481,24 @@
         <v>80</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6518,19 +6521,19 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -6579,7 +6582,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>90</v>
@@ -6594,30 +6597,30 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6643,16 +6646,16 @@
         <v>188</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -6701,7 +6704,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6725,10 +6728,10 @@
         <v>80</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>80</v>
@@ -6736,10 +6739,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6765,16 +6768,16 @@
         <v>212</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>80</v>
@@ -6802,10 +6805,10 @@
         <v>217</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>80</v>
@@ -6823,7 +6826,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6847,7 +6850,7 @@
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>80</v>
@@ -6858,10 +6861,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6887,16 +6890,16 @@
         <v>242</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -6945,7 +6948,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6960,19 +6963,19 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>80</v>
@@ -6980,10 +6983,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7006,19 +7009,19 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -7067,7 +7070,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>90</v>
@@ -7088,24 +7091,24 @@
         <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7128,19 +7131,19 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
@@ -7189,7 +7192,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7224,10 +7227,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7342,10 +7345,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7462,14 +7465,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7491,10 +7494,10 @@
         <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>165</v>
@@ -7549,7 +7552,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7584,10 +7587,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7613,16 +7616,16 @@
         <v>212</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -7650,10 +7653,10 @@
         <v>217</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>80</v>
@@ -7671,7 +7674,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>90</v>
@@ -7706,10 +7709,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7735,16 +7738,16 @@
         <v>188</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -7793,7 +7796,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>90</v>
@@ -7817,21 +7820,21 @@
         <v>80</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7857,14 +7860,14 @@
         <v>188</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -7913,7 +7916,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7937,21 +7940,21 @@
         <v>80</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7974,19 +7977,19 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8035,7 +8038,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8062,7 +8065,7 @@
         <v>80</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>80</v>
@@ -8070,10 +8073,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8099,14 +8102,14 @@
         <v>188</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -8155,7 +8158,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8179,7 +8182,7 @@
         <v>80</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>80</v>
@@ -8190,14 +8193,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8216,19 +8219,19 @@
         <v>80</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8277,7 +8280,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8312,10 +8315,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8430,10 +8433,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8550,14 +8553,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8579,10 +8582,10 @@
         <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>165</v>
@@ -8637,7 +8640,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8672,10 +8675,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8701,16 +8704,16 @@
         <v>212</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>80</v>
@@ -8738,10 +8741,10 @@
         <v>217</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>80</v>
@@ -8759,7 +8762,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8794,10 +8797,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8912,10 +8915,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9032,10 +9035,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9058,19 +9061,19 @@
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
@@ -9119,7 +9122,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9137,7 +9140,7 @@
         <v>80</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>80</v>
@@ -9146,7 +9149,7 @@
         <v>80</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>80</v>
@@ -9154,10 +9157,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9272,10 +9275,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9392,10 +9395,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9421,16 +9424,16 @@
         <v>104</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>80</v>
@@ -9479,7 +9482,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9497,7 +9500,7 @@
         <v>80</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>80</v>
@@ -9506,7 +9509,7 @@
         <v>80</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>80</v>
@@ -9514,10 +9517,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9543,13 +9546,13 @@
         <v>188</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9599,7 +9602,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9617,7 +9620,7 @@
         <v>80</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>80</v>
@@ -9626,7 +9629,7 @@
         <v>80</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>80</v>
@@ -9634,10 +9637,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9663,16 +9666,16 @@
         <v>110</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>80</v>
@@ -9721,7 +9724,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9739,7 +9742,7 @@
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>80</v>
@@ -9748,7 +9751,7 @@
         <v>80</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>80</v>
@@ -9756,10 +9759,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9785,14 +9788,14 @@
         <v>188</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -9841,7 +9844,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9859,7 +9862,7 @@
         <v>80</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>80</v>
@@ -9868,7 +9871,7 @@
         <v>80</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>80</v>
@@ -9876,10 +9879,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9902,19 +9905,19 @@
         <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>80</v>
@@ -9963,7 +9966,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -9981,7 +9984,7 @@
         <v>80</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>80</v>
@@ -9990,7 +9993,7 @@
         <v>80</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>80</v>
@@ -9998,10 +10001,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10027,16 +10030,16 @@
         <v>188</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>80</v>
@@ -10085,7 +10088,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10103,7 +10106,7 @@
         <v>80</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>80</v>
@@ -10112,7 +10115,7 @@
         <v>80</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>80</v>
@@ -10120,10 +10123,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10146,19 +10149,19 @@
         <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10207,7 +10210,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>90</v>
@@ -10231,21 +10234,21 @@
         <v>80</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10268,17 +10271,17 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>80</v>
@@ -10327,7 +10330,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10362,10 +10365,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10480,10 +10483,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10600,14 +10603,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10629,10 +10632,10 @@
         <v>135</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>165</v>
@@ -10687,7 +10690,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10722,10 +10725,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10751,14 +10754,14 @@
         <v>212</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>80</v>
@@ -10783,13 +10786,13 @@
         <v>80</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>80</v>
@@ -10807,7 +10810,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>90</v>
@@ -10842,10 +10845,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10871,14 +10874,14 @@
         <v>242</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>80</v>
@@ -10927,7 +10930,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10962,10 +10965,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10988,19 +10991,19 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>80</v>
@@ -11049,7 +11052,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11084,10 +11087,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11110,19 +11113,19 @@
         <v>80</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>80</v>
@@ -11171,7 +11174,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11195,13 +11198,13 @@
         <v>80</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>

--- a/jpcore-r4/feature/add_coverage_identifier/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/feature/add_coverage_identifier/StructureDefinition-jp-coverage.xlsx
@@ -822,7 +822,7 @@
     <t>insuranceCsvIdentifier</t>
   </si>
   <si>
-    <t>被保険者識別子（CSV形式）　"１２－３４","５６７８","00"</t>
+    <t>被保険者識別子（CSV形式）　"00012345","１２－３４","５６７８","00"</t>
   </si>
   <si>
     <t>被保険者識別子として、保険者情報と被保険者情報をカンマ区切りにて連結する</t>
@@ -831,8 +831,8 @@
     <t>The main (and possibly only) identifier for the coverage - often referred to as a Member Id, Certificate number, Personal Health Number or Case ID. May be constructed as the concatenation of the Coverage.SubscriberID and the Coverage.dependent.  
 カバレッジのメイン（および場合によっては唯一の）識別子-多くの場合、メンバID、証明書番号、個人の健康番号、またはケースIDと呼ばれる。  
 【JP Core仕様】被保険者記号と番号と枝番を全角にした上でダブルコーテーションで囲い、カンマ区切りで連結する。  
-ルール："{被保険者記号}","{被保険者番号}","{枝番}"  
-例："１２－３４","５６７８","00"</t>
+ルール："{保険者番号:半角英数８桁}","{被保険者記号}","{被保険者番号}","{枝番:半角数字２桁}"  
+例："00012345","１２－３４","５６７８","00"</t>
   </si>
   <si>
     <t>Coverage.identifier:insuranceCsvIdentifier.id</t>
@@ -861,7 +861,7 @@
 【JP Core仕様】被保険者記号と番号と枝番を全角にした上でダブルコーテーションで囲い、カンマ区切りで連結する。  
 ルール："{保険者番号:半角英数８桁}","{被保険者記号}","{被保険者番号}","{枝番:半角数字２桁}"  
 例："00012345","１２－３４","５６７８","00"
-要素を省略する、とある場合には、長さ０の文字列とする。「被保険者識別子」の文字列仕様(StructureDefinition_JP_Coverage.html#「被保険者識別子」の文字列仕様)を参照のこと</t>
+要素を省略する、とある場合には、長さ０の文字列とする。</t>
   </si>
   <si>
     <t>Coverage.identifier:insuranceCsvIdentifier.period</t>
